--- a/entregables/SIGRO - Sprint Backlog 1.xlsx
+++ b/entregables/SIGRO - Sprint Backlog 1.xlsx
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="G33" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H33" s="15" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>7</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
@@ -2020,7 +2020,7 @@
         <v>4</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
